--- a/sports_forms/001_pool_chemicals_check_form--sports_forms.xlsx
+++ b/sports_forms/001_pool_chemicals_check_form--sports_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pool Chemicals Check</t>
+          <t>Pool Chemicals Check Form</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>chemicals</t>
+          <t>pool_maintenance_chemicals</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>What is the current chemical used for pool maintenance?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>chemical_1</t>
+          <t>algaecide</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>chemical_2</t>
+          <t>stabilizer</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>chemical_3</t>
+          <t>clarifier</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>chemical_4</t>
+          <t>other_chemicals</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algaecide</t>
+          <t>Other chemicals</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>chemical_5</t>
+          <t>other_chemicals_used</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Stabilizer</t>
+          <t>What are these other chemicals?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>chemical_6</t>
+          <t>chemical_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Clarifier</t>
+          <t>What is the brand name of the pool chemicals used?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>other_chemicals</t>
+          <t>algaecide_expiration</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Other chemicals</t>
+          <t>What is the expiration date of the Algaecide?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,23 +722,69 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>other_chemicals_1</t>
+          <t>stabilizer_expiration</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Other chemicals 1</t>
+          <t>What is the expiration date of the Stabilizer?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>clarifier_expiration</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>What is the expiration date of the Clarifier?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>pool_check</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Pool Check</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -753,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -781,58 +827,58 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>chemicals_choices</t>
+          <t>pool_maintenance_chemicals_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>algaecide</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Algaecide</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>chemicals_choices</t>
+          <t>pool_maintenance_chemicals_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stabilizer</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Stabilizer</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>chemical_1_choices</t>
+          <t>pool_maintenance_chemicals_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>algaecide</t>
+          <t>clarifier</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Algaecide</t>
+          <t>Clarifier</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>chemical_1_choices</t>
+          <t>algaecide_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -849,24 +895,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>chemical_1_choices</t>
+          <t>algaecide_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>algaecide</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algaecide</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>chemical_2_choices</t>
+          <t>stabilizer_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -883,323 +929,85 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>chemical_2_choices</t>
+          <t>stabilizer_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>stabilizer</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Stabilizer</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>chemical_2_choices</t>
+          <t>clarifier_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>stabilizer</t>
+          <t>clarifier</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Stabilizer</t>
+          <t>Clarifier</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>chemical_3_choices</t>
+          <t>clarifier_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>clarifier</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Clarifier</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>chemical_3_choices</t>
+          <t>other_chemicals_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>clarifier</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Clarifier</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>chemical_3_choices</t>
+          <t>other_chemicals_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>clarifier</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Clarifier</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>chemical_4_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>algaecide</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Algaecide</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>chemical_4_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>algaecide</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Algaecide</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>chemical_4_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>algaecide</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Algaecide</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>chemical_5_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>stabilizer</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Stabilizer</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>chemical_5_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>stabilizer</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Stabilizer</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>chemical_5_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>stabilizer</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Stabilizer</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>chemical_6_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>clarifier</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Clarifier</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>chemical_6_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>clarifier</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Clarifier</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>chemical_6_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>clarifier</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Clarifier</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>other_chemicals_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>other_chemicals_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>other_chemicals_1_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>other_chemicals_1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Other chemicals 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>other_chemicals_1_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>other_chemicals_1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Other chemicals 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>other_chemicals_1_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>other_chemicals_1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Other chemicals 1</t>
+          <t>False</t>
         </is>
       </c>
     </row>
